--- a/sheets/대금율보/검수/합주곡1번 中.xlsx
+++ b/sheets/대금율보/검수/합주곡1번 中.xlsx
@@ -2367,22 +2367,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -2677,7 +2677,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2771,7 +2771,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2784,7 +2784,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2827,6 +2827,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>